--- a/Test/Test Suite/TestPlanPrincipleController.xlsx
+++ b/Test/Test Suite/TestPlanPrincipleController.xlsx
@@ -23,7 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Aptos Narrow"/>
@@ -84,7 +86,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -325,11 +327,32 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -454,6 +477,26 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -851,7 +894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="21.77734375" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -859,7 +902,7 @@
     <col width="18.109375" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
     <col width="8.88671875" customWidth="1" style="2" min="4" max="5"/>
     <col width="22" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
-    <col width="8.88671875" customWidth="1" style="2" min="7" max="16384"/>
+    <col width="17" customWidth="1" style="2" min="7" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -917,6 +960,11 @@
           <t>Relative Defects (ID)</t>
         </is>
       </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Line Coverage (%)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="39" t="inlineStr">
@@ -932,9 +980,16 @@
       <c r="C6" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="39" t="n"/>
-      <c r="E6" s="39" t="n"/>
+      <c r="D6" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F6" s="39" t="n"/>
+      <c r="G6" s="57" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="39" t="inlineStr">
@@ -950,9 +1005,14 @@
       <c r="C7" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="39" t="n"/>
-      <c r="E7" s="39" t="n"/>
+      <c r="D7" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F7" s="39" t="n"/>
+      <c r="G7" s="58" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="39" t="inlineStr">
@@ -968,9 +1028,14 @@
       <c r="C8" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="39" t="n"/>
-      <c r="E8" s="39" t="n"/>
+      <c r="D8" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F8" s="39" t="n"/>
+      <c r="G8" s="58" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="39" t="inlineStr">
@@ -986,9 +1051,14 @@
       <c r="C9" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="39" t="n"/>
-      <c r="E9" s="39" t="n"/>
+      <c r="D9" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F9" s="39" t="n"/>
+      <c r="G9" s="58" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="39" t="inlineStr">
@@ -1004,9 +1074,14 @@
       <c r="C10" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="39" t="n"/>
-      <c r="E10" s="39" t="n"/>
+      <c r="D10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F10" s="39" t="n"/>
+      <c r="G10" s="58" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="39" t="inlineStr">
@@ -1022,9 +1097,14 @@
       <c r="C11" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="39" t="n"/>
-      <c r="E11" s="39" t="n"/>
+      <c r="D11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F11" s="39" t="n"/>
+      <c r="G11" s="58" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="39" t="inlineStr">
@@ -1040,9 +1120,14 @@
       <c r="C12" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="39" t="n"/>
-      <c r="E12" s="39" t="n"/>
+      <c r="D12" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F12" s="39" t="n"/>
+      <c r="G12" s="58" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="39" t="inlineStr">
@@ -1058,9 +1143,14 @@
       <c r="C13" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="39" t="n"/>
-      <c r="E13" s="39" t="n"/>
+      <c r="D13" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F13" s="39" t="n"/>
+      <c r="G13" s="59" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="39" t="inlineStr">
@@ -1076,9 +1166,16 @@
       <c r="C14" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="39" t="n"/>
-      <c r="E14" s="39" t="n"/>
+      <c r="D14" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F14" s="39" t="n"/>
+      <c r="G14" s="39" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="47" t="inlineStr">
@@ -1094,9 +1191,16 @@
       <c r="C15" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="39" t="n"/>
-      <c r="E15" s="39" t="n"/>
+      <c r="D15" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F15" s="39" t="n"/>
+      <c r="G15" s="57" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="39" t="inlineStr">
@@ -1112,9 +1216,14 @@
       <c r="C16" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="39" t="n"/>
-      <c r="E16" s="39" t="n"/>
+      <c r="D16" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F16" s="39" t="n"/>
+      <c r="G16" s="59" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="39" t="inlineStr">
@@ -1130,9 +1239,16 @@
       <c r="C17" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="39" t="n"/>
-      <c r="E17" s="39" t="n"/>
+      <c r="D17" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F17" s="39" t="n"/>
+      <c r="G17" s="57" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="39" t="inlineStr">
@@ -1148,9 +1264,14 @@
       <c r="C18" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="39" t="n"/>
-      <c r="E18" s="39" t="n"/>
+      <c r="D18" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F18" s="39" t="n"/>
+      <c r="G18" s="58" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="39" t="inlineStr">
@@ -1166,9 +1287,14 @@
       <c r="C19" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="39" t="n"/>
-      <c r="E19" s="39" t="n"/>
+      <c r="D19" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F19" s="39" t="n"/>
+      <c r="G19" s="58" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="39" t="inlineStr">
@@ -1184,9 +1310,18 @@
       <c r="C20" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="39" t="n"/>
-      <c r="E20" s="39" t="n"/>
-      <c r="F20" s="39" t="n"/>
+      <c r="D20" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="39" t="inlineStr">
+        <is>
+          <t>DEF-CTL-01</t>
+        </is>
+      </c>
+      <c r="G20" s="59" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="39" t="inlineStr">
@@ -1202,9 +1337,20 @@
       <c r="C21" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="39" t="n"/>
-      <c r="E21" s="39" t="n"/>
-      <c r="F21" s="39" t="n"/>
+      <c r="D21" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="39" t="inlineStr">
+        <is>
+          <t>DEF-CTL-02, DEF-CTL-01</t>
+        </is>
+      </c>
+      <c r="G21" s="39" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="39" t="inlineStr">
@@ -1220,9 +1366,16 @@
       <c r="C22" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="39" t="n"/>
-      <c r="E22" s="39" t="n"/>
+      <c r="D22" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F22" s="39" t="n"/>
+      <c r="G22" s="57" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="39" t="inlineStr">
@@ -1238,9 +1391,14 @@
       <c r="C23" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="39" t="n"/>
-      <c r="E23" s="39" t="n"/>
+      <c r="D23" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F23" s="39" t="n"/>
+      <c r="G23" s="59" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="39" t="inlineStr">
@@ -1256,9 +1414,18 @@
       <c r="C24" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="39" t="n"/>
-      <c r="E24" s="39" t="n"/>
+      <c r="D24" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F24" s="39" t="n"/>
+      <c r="G24" s="57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="39" t="inlineStr">
@@ -1274,9 +1441,14 @@
       <c r="C25" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="39" t="n"/>
-      <c r="E25" s="39" t="n"/>
+      <c r="D25" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F25" s="39" t="n"/>
+      <c r="G25" s="58" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="39" t="inlineStr">
@@ -1292,9 +1464,14 @@
       <c r="C26" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="39" t="n"/>
-      <c r="E26" s="39" t="n"/>
+      <c r="D26" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F26" s="39" t="n"/>
+      <c r="G26" s="58" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="39" t="inlineStr">
@@ -1310,9 +1487,14 @@
       <c r="C27" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="39" t="n"/>
-      <c r="E27" s="39" t="n"/>
+      <c r="D27" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F27" s="39" t="n"/>
+      <c r="G27" s="58" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="39" t="inlineStr">
@@ -1328,9 +1510,14 @@
       <c r="C28" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="39" t="n"/>
-      <c r="E28" s="39" t="n"/>
+      <c r="D28" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F28" s="39" t="n"/>
+      <c r="G28" s="58" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="39" t="inlineStr">
@@ -1346,9 +1533,14 @@
       <c r="C29" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="39" t="n"/>
-      <c r="E29" s="39" t="n"/>
+      <c r="D29" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="39" t="n">
+        <v>0</v>
+      </c>
       <c r="F29" s="39" t="n"/>
+      <c r="G29" s="59" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="39" t="inlineStr">
@@ -1360,13 +1552,29 @@
       <c r="C30" s="39" t="n">
         <v>28</v>
       </c>
-      <c r="D30" s="41" t="n"/>
-      <c r="E30" s="41" t="n"/>
-      <c r="F30" s="41" t="n"/>
+      <c r="D30" s="41" t="n">
+        <v>26</v>
+      </c>
+      <c r="E30" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="41" t="inlineStr">
+        <is>
+          <t>DEF-CTL-01, DEF-CTL-02</t>
+        </is>
+      </c>
+      <c r="G30" s="41" t="n">
+        <v>90</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="6">
+    <mergeCell ref="G6:G13"/>
+    <mergeCell ref="G22:G23"/>
     <mergeCell ref="A30:B30"/>
+    <mergeCell ref="G17:G20"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="G24:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1383,11 +1591,11 @@
   <cols>
     <col width="4.33203125" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
     <col width="9.88671875" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
-    <col width="12" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
-    <col width="12.77734375" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
-    <col width="8.21875" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
-    <col width="13.21875" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
-    <col width="34.44140625" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
+    <col width="30" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="52" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="60" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="13" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
+    <col width="14" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1427,27 +1635,71 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="72" customHeight="1">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-    </row>
-    <row r="3">
+      <c r="B2" s="52" t="inlineStr">
+        <is>
+          <t>DEF-CTL-01</t>
+        </is>
+      </c>
+      <c r="C2" s="53" t="inlineStr">
+        <is>
+          <t>Business errors answer 409 where the suite documents 400</t>
+        </is>
+      </c>
+      <c r="D2" s="53" t="inlineStr">
+        <is>
+          <t>GlobalExceptionHandler maps BusinessLogicException to HTTP 409 CONFLICT, but MarshalDraftController TC04 and PlacementController TC02 document HTTP 400.</t>
+        </is>
+      </c>
+      <c r="E2" s="53" t="inlineStr">
+        <is>
+          <t>Observed 409 + body message 'No rerolls remain' and 409 + body message 'Game is not in placement phase'. Either the suite should read 409 or validation failures should be routed to 400.</t>
+        </is>
+      </c>
+      <c r="F2" s="56" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G2" s="53" t="inlineStr">
+        <is>
+          <t>Opened</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="72" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
+      <c r="B3" s="52" t="inlineStr">
+        <is>
+          <t>DEF-CTL-02</t>
+        </is>
+      </c>
+      <c r="C3" s="53" t="inlineStr">
+        <is>
+          <t>Placement endpoint has no request body</t>
+        </is>
+      </c>
+      <c r="D3" s="53" t="inlineStr">
+        <is>
+          <t>PlacementController TC01 documents playerId and cityId as a JSON body; the handler binds them as @RequestParam, so the documented request cannot produce the documented response.</t>
+        </is>
+      </c>
+      <c r="E3" s="53" t="inlineStr">
+        <is>
+          <t>The test posts query parameters to get 200 with an empty body. A JSON body POST fails with 400 (missing required parameter). API contract and test suite need to agree.</t>
+        </is>
+      </c>
+      <c r="F3" s="56" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G3" s="53" t="inlineStr">
+        <is>
+          <t>Opened</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1500,7 +1752,7 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1547,7 +1799,7 @@
       </c>
       <c r="B5" s="43" t="inlineStr">
         <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
         </is>
       </c>
       <c r="C5" s="51" t="n"/>
@@ -1625,7 +1877,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="43" t="inlineStr">
         <is>
           <t>TC01</t>
@@ -1646,11 +1898,19 @@
           <t>HTTP 201 CREATED; body roomCode == 'TEST99'</t>
         </is>
       </c>
-      <c r="E12" s="43" t="n"/>
-      <c r="F12" s="43" t="n"/>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 201 CREATED with body roomCode 'TEST99'</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G12" s="43" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="43" t="inlineStr">
         <is>
           <t>TC02</t>
@@ -1671,11 +1931,19 @@
           <t>HTTP 200 OK; body status == MARSHAL_SELECTION</t>
         </is>
       </c>
-      <c r="E13" s="43" t="n"/>
-      <c r="F13" s="43" t="n"/>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK with body status MARSHAL_SELECTION</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G13" s="43" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="43" t="inlineStr">
         <is>
           <t>TC03</t>
@@ -1696,11 +1964,19 @@
           <t>HTTP 200; body id == 1, status IN_PROGRESS</t>
         </is>
       </c>
-      <c r="E14" s="43" t="n"/>
-      <c r="F14" s="43" t="n"/>
+      <c r="E14" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK with body id 1 and status IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="F14" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G14" s="43" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="18" customHeight="1">
       <c r="A15" s="43" t="inlineStr">
         <is>
           <t>TC04</t>
@@ -1721,11 +1997,19 @@
           <t>HTTP 200 with that game</t>
         </is>
       </c>
-      <c r="E15" s="43" t="n"/>
-      <c r="F15" s="43" t="n"/>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK with body roomCode 'ABC123'</t>
+        </is>
+      </c>
+      <c r="F15" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G15" s="43" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="108" customHeight="1">
       <c r="A16" s="43" t="inlineStr">
         <is>
           <t>TC05</t>
@@ -1746,11 +2030,19 @@
           <t>HTTP 404</t>
         </is>
       </c>
-      <c r="E16" s="43" t="n"/>
-      <c r="F16" s="43" t="n"/>
+      <c r="E16" s="55" t="inlineStr">
+        <is>
+          <t>the controller lets ResourceNotFoundException('Game not found with room code: NOPE') propagate; the HTTP 404 is produced by GlobalExceptionHandler, which is asserted end-to-end in PlayerController TC02</t>
+        </is>
+      </c>
+      <c r="F16" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G16" s="43" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="36" customHeight="1">
       <c r="A17" s="43" t="inlineStr">
         <is>
           <t>TC06</t>
@@ -1771,11 +2063,19 @@
           <t>HTTP 201 with the player dto</t>
         </is>
       </c>
-      <c r="E17" s="43" t="n"/>
-      <c r="F17" s="43" t="n"/>
+      <c r="E17" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 201 CREATED with body id 100</t>
+        </is>
+      </c>
+      <c r="F17" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G17" s="43" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="43" t="inlineStr">
         <is>
           <t>TC07</t>
@@ -1796,11 +2096,19 @@
           <t>HTTP 200; list length 2</t>
         </is>
       </c>
-      <c r="E18" s="43" t="n"/>
-      <c r="F18" s="43" t="n"/>
+      <c r="E18" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK with a list of 2 players</t>
+        </is>
+      </c>
+      <c r="F18" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G18" s="43" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="43" t="inlineStr">
         <is>
           <t>TC08</t>
@@ -1821,11 +2129,19 @@
           <t>HTTP 200; paged list with 10 items per page</t>
         </is>
       </c>
-      <c r="E19" s="43" t="n"/>
-      <c r="F19" s="43" t="n"/>
+      <c r="E19" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; page content size 10 and pageable page size 10</t>
+        </is>
+      </c>
+      <c r="F19" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G19" s="43" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="43" t="inlineStr">
         <is>
           <t>TC09</t>
@@ -1846,8 +2162,16 @@
           <t>HTTP 200 with cities, edges and players</t>
         </is>
       </c>
-      <c r="E20" s="43" t="n"/>
-      <c r="F20" s="43" t="n"/>
+      <c r="E20" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK with 1 map node, 1 edge and 1 player in the snapshot</t>
+        </is>
+      </c>
+      <c r="F20" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G20" s="43" t="n"/>
     </row>
   </sheetData>
@@ -1875,7 +2199,7 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1922,7 +2246,7 @@
       </c>
       <c r="B5" s="43" t="inlineStr">
         <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
         </is>
       </c>
       <c r="C5" s="51" t="n"/>
@@ -2000,7 +2324,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="43" t="inlineStr">
         <is>
           <t>TC01</t>
@@ -2021,11 +2345,19 @@
           <t>HTTP 201; status WAITING; playerCount 0; alivePlayerCount 0</t>
         </is>
       </c>
-      <c r="E12" s="43" t="n"/>
-      <c r="F12" s="43" t="n"/>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 201; JSON status WAITING, playerCount 0, alivePlayerCount 0</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G12" s="43" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="43" t="inlineStr">
         <is>
           <t>TC02</t>
@@ -2046,11 +2378,19 @@
           <t>HTTP 200; gameId 10; name 'Pizza'; marshal.name 'โจโฉ'; game and city not serialized</t>
         </is>
       </c>
-      <c r="E13" s="43" t="n"/>
-      <c r="F13" s="43" t="n"/>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200; gameId 10, name 'Pizza', marshal.name 'โจโฉ' and no 'game' or 'city' property in the JSON</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G13" s="43" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="43" t="inlineStr">
         <is>
           <t>TC03</t>
@@ -2071,11 +2411,19 @@
           <t>HTTP 400; status 400</t>
         </is>
       </c>
-      <c r="E14" s="43" t="n"/>
-      <c r="F14" s="43" t="n"/>
+      <c r="E14" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 400 with body status 400 (blank @NotBlank name)</t>
+        </is>
+      </c>
+      <c r="F14" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G14" s="43" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="72" customHeight="1">
       <c r="A15" s="43" t="inlineStr">
         <is>
           <t>TC04</t>
@@ -2096,11 +2444,19 @@
           <t>HTTP 201; turnNumber 3; actionType SEND_ARMY; armyId 11; soldiersAfter 80</t>
         </is>
       </c>
-      <c r="E15" s="43" t="n"/>
-      <c r="F15" s="43" t="n"/>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 201; turnNumber 3, actionType SEND_ARMY, armyId 11, soldiersAfter 80</t>
+        </is>
+      </c>
+      <c r="F15" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G15" s="43" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="43" t="inlineStr">
         <is>
           <t>TC05</t>
@@ -2121,11 +2477,19 @@
           <t>HTTP 200; slotNumber 2; marshal.name 'ลิโป้'</t>
         </is>
       </c>
-      <c r="E16" s="43" t="n"/>
-      <c r="F16" s="43" t="n"/>
+      <c r="E16" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200; slotNumber 2 and marshal.name 'ลิโป้'</t>
+        </is>
+      </c>
+      <c r="F16" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G16" s="43" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="72" customHeight="1">
       <c r="A17" s="43" t="inlineStr">
         <is>
           <t>TC06</t>
@@ -2146,8 +2510,16 @@
           <t>HTTP 200; only game 1 rows; ?turnNumber=4 -&gt; 1 item, cityDestroyed true</t>
         </is>
       </c>
-      <c r="E17" s="43" t="n"/>
-      <c r="F17" s="43" t="n"/>
+      <c r="E17" s="55" t="inlineStr">
+        <is>
+          <t>GET /api/games/1/battles returns only battle 31 (game 2's battle 32 is filtered out); ?turnNumber=4 gives 1 item with cityDestroyed true</t>
+        </is>
+      </c>
+      <c r="F17" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G17" s="43" t="n"/>
     </row>
   </sheetData>
@@ -2175,7 +2547,7 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2222,7 +2594,7 @@
       </c>
       <c r="B5" s="43" t="inlineStr">
         <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
         </is>
       </c>
       <c r="C5" s="51" t="n"/>
@@ -2300,7 +2672,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="54" customHeight="1">
       <c r="A12" s="43" t="inlineStr">
         <is>
           <t>TC01</t>
@@ -2321,11 +2693,19 @@
           <t>HTTP 201 CREATED; body id == 50</t>
         </is>
       </c>
-      <c r="E12" s="43" t="n"/>
-      <c r="F12" s="43" t="n"/>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 201 CREATED with body id 50</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G12" s="43" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="43" t="inlineStr">
         <is>
           <t>TC02</t>
@@ -2346,11 +2726,19 @@
           <t>HTTP 201; dto carries armyId</t>
         </is>
       </c>
-      <c r="E13" s="43" t="n"/>
-      <c r="F13" s="43" t="n"/>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 201 CREATED with body armyId 11</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G13" s="43" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="43" t="inlineStr">
         <is>
           <t>TC03</t>
@@ -2371,8 +2759,16 @@
           <t>HTTP 200; body currentTurnNumber == 2</t>
         </is>
       </c>
-      <c r="E14" s="43" t="n"/>
-      <c r="F14" s="43" t="n"/>
+      <c r="E14" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK with body currentTurnNumber 2</t>
+        </is>
+      </c>
+      <c r="F14" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G14" s="43" t="n"/>
     </row>
   </sheetData>
@@ -2400,7 +2796,7 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2447,7 +2843,7 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
         </is>
       </c>
       <c r="C5" s="51" t="n"/>
@@ -2525,7 +2921,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="54" customHeight="1">
       <c r="A12" s="43" t="inlineStr">
         <is>
           <t>TC01</t>
@@ -2546,11 +2942,19 @@
           <t>HTTP 200; gameId 10; name 'Pizza'; marshal.name 'โจโฉ'; game and city fields absent</t>
         </is>
       </c>
-      <c r="E12" s="43" t="n"/>
-      <c r="F12" s="43" t="n"/>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200; gameId 10, name 'Pizza', marshal.name 'โจโฉ', game and city properties absent</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G12" s="43" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="43" t="inlineStr">
         <is>
           <t>TC02</t>
@@ -2571,8 +2975,16 @@
           <t>HTTP 404</t>
         </is>
       </c>
-      <c r="E13" s="43" t="n"/>
-      <c r="F13" s="43" t="n"/>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 404 with body status 404</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G13" s="43" t="n"/>
     </row>
   </sheetData>
@@ -2600,7 +3012,7 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2647,7 +3059,7 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
         </is>
       </c>
       <c r="C5" s="51" t="n"/>
@@ -2725,7 +3137,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="43" t="inlineStr">
         <is>
           <t>TC01</t>
@@ -2746,11 +3158,19 @@
           <t>HTTP 200; slotNumber 2; marshal.name 'ลิโป้'</t>
         </is>
       </c>
-      <c r="E12" s="43" t="n"/>
-      <c r="F12" s="43" t="n"/>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200; slotNumber 2 and marshal.name 'ลิโป้'</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G12" s="43" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="43" t="inlineStr">
         <is>
           <t>TC02</t>
@@ -2771,11 +3191,19 @@
           <t>HTTP 200; list length 3</t>
         </is>
       </c>
-      <c r="E13" s="43" t="n"/>
-      <c r="F13" s="43" t="n"/>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200 with a list of 3 candidates</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G13" s="43" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="43" t="inlineStr">
         <is>
           <t>TC03</t>
@@ -2796,11 +3224,19 @@
           <t>HTTP 200 with the marshal dto</t>
         </is>
       </c>
-      <c r="E14" s="43" t="n"/>
-      <c r="F14" s="43" t="n"/>
+      <c r="E14" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200 with the chosen marshal dto (id 22, name 'ลิโป้')</t>
+        </is>
+      </c>
+      <c r="F14" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G14" s="43" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="43" t="inlineStr">
         <is>
           <t>TC04</t>
@@ -2821,9 +3257,21 @@
           <t>HTTP 400 with the error body</t>
         </is>
       </c>
-      <c r="E15" s="43" t="n"/>
-      <c r="F15" s="43" t="n"/>
-      <c r="G15" s="43" t="n"/>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 409 CONFLICT with body message 'No rerolls remain', not the documented 400</t>
+        </is>
+      </c>
+      <c r="F15" s="43" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G15" s="43" t="inlineStr">
+        <is>
+          <t>DEF-CTL-01</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2850,7 +3298,7 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2897,7 +3345,7 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
         </is>
       </c>
       <c r="C5" s="51" t="n"/>
@@ -2975,7 +3423,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="43" t="inlineStr">
         <is>
           <t>TC01</t>
@@ -2996,11 +3444,23 @@
           <t>HTTP 200/204 with no body</t>
         </is>
       </c>
-      <c r="E12" s="43" t="n"/>
-      <c r="F12" s="43" t="n"/>
-      <c r="G12" s="43" t="n"/>
-    </row>
-    <row r="13">
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200 with an empty body and selectBase(1L, 1L, 1L) called - but only when playerId and cityId are sent as query parameters; the endpoint has no JSON request body</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="43" t="inlineStr">
+        <is>
+          <t>DEF-CTL-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="43" t="inlineStr">
         <is>
           <t>TC02</t>
@@ -3021,9 +3481,21 @@
           <t>HTTP 400</t>
         </is>
       </c>
-      <c r="E13" s="43" t="n"/>
-      <c r="F13" s="43" t="n"/>
-      <c r="G13" s="43" t="n"/>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 409 CONFLICT with body message 'Game is not in placement phase', not the documented 400</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G13" s="43" t="inlineStr">
+        <is>
+          <t>DEF-CTL-01</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3050,7 +3522,7 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
@@ -3097,7 +3569,7 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
         </is>
       </c>
       <c r="C5" s="51" t="n"/>
@@ -3175,7 +3647,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="72" customHeight="1">
       <c r="A12" s="43" t="inlineStr">
         <is>
           <t>TC01</t>
@@ -3196,11 +3668,19 @@
           <t>HTTP 200; only game 1 battles; with ?turnNumber=4 -&gt; 1 item, cityDestroyed true</t>
         </is>
       </c>
-      <c r="E12" s="43" t="n"/>
-      <c r="F12" s="43" t="n"/>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200: unfiltered returns only battle 31 of game 1; ?turnNumber=4 -&gt; 1 item with cityDestroyed true; ?turnNumber=5 -&gt; empty list</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G12" s="43" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="43" t="inlineStr">
         <is>
           <t>TC02</t>
@@ -3221,8 +3701,16 @@
           <t>HTTP 200; list filtered by game (and turn when supplied)</t>
         </is>
       </c>
-      <c r="E13" s="43" t="n"/>
-      <c r="F13" s="43" t="n"/>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>HTTP 200: game 1 -&gt; 2 events; ?turnNumber=3 -&gt; 2 events, first eventType EPIDEMIC; ?turnNumber=8 -&gt; empty list</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="G13" s="43" t="n"/>
     </row>
   </sheetData>
